--- a/data/trans_orig/IP07B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07B-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores según su salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30564</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27301</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54106</t>
+          <t>53587</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,43%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>31794</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50183</t>
+          <t>49647</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40944</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60870</t>
+          <t>60032</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77611</t>
+          <t>77171</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103907</t>
+          <t>103626</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96626</t>
+          <t>97077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118619</t>
+          <t>117865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113203</t>
+          <t>113193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135316</t>
+          <t>136274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214420</t>
+          <t>216878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>248423</t>
+          <t>250507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25739</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42935</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24204</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40670</t>
+          <t>40803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53861</t>
+          <t>55287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78335</t>
+          <t>78679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26434</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>36257</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>55506</t>
+          <t>55954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71509</t>
+          <t>71098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16035</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29991</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70200</t>
+          <t>69797</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>81319</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>112821</t>
+          <t>111046</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>144794</t>
+          <t>142730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>149058</t>
+          <t>148734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175001</t>
+          <t>175311</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166420</t>
+          <t>165446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>193474</t>
+          <t>193116</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322098</t>
+          <t>324773</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>360250</t>
+          <t>362301</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46887</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68555</t>
+          <t>68577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37539</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>118263</t>
+          <t>118681</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores según su salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7624</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>17159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19718</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>44537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60897</t>
+          <t>59998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22653</t>
+          <t>21973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48188</t>
+          <t>48319</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38103</t>
+          <t>37228</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57344</t>
+          <t>58154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>72291</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100718</t>
+          <t>99282</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98296</t>
+          <t>97240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120849</t>
+          <t>120150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95691</t>
+          <t>96517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119168</t>
+          <t>120329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199355</t>
+          <t>201565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>232988</t>
+          <t>234535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42859</t>
+          <t>43443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38991</t>
+          <t>38338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59077</t>
+          <t>58069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69297</t>
+          <t>68187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96327</t>
+          <t>95422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26663</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42656</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>24707</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>37438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,49 +5410,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>64,78%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>28633</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>21646</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>34237</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>54,11%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>64,7%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>28633</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>23352</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>33748</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>44,13%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>63,78%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>86</t>
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50880</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68823</t>
+          <t>68538</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>63296</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86258</t>
+          <t>86929</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63508</t>
+          <t>62097</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88789</t>
+          <t>86620</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>132284</t>
+          <t>131934</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>168315</t>
+          <t>167938</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>152939</t>
+          <t>153292</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180187</t>
+          <t>178790</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>147279</t>
+          <t>148479</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177639</t>
+          <t>175897</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>306806</t>
+          <t>309544</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>347468</t>
+          <t>350592</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33233</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>52746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>90389</t>
+          <t>90933</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>121135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores según su salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17839</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>25830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27409</t>
+          <t>27048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,38%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>26973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24460</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42291</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28696</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45902</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56015</t>
+          <t>57653</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83342</t>
+          <t>83527</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99015</t>
+          <t>97678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122836</t>
+          <t>123062</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70805</t>
+          <t>70370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95404</t>
+          <t>95180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176656</t>
+          <t>177139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211735</t>
+          <t>211827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70357</t>
+          <t>70482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94346</t>
+          <t>94328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83457</t>
+          <t>82594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106890</t>
+          <t>106626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159849</t>
+          <t>158653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193764</t>
+          <t>193606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26789</t>
+          <t>26743</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>25762</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>39393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61550</t>
+          <t>60851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>81611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,33%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>25704</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34360</t>
+          <t>33979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>37299</t>
+          <t>36695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55620</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>36801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59008</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63979</t>
+          <t>64677</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84241</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115265</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147619</t>
+          <t>146168</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177654</t>
+          <t>176316</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122116</t>
+          <t>121741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>152581</t>
+          <t>151631</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>279496</t>
+          <t>277304</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>320525</t>
+          <t>320344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96434</t>
+          <t>97139</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>125365</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>116209</t>
+          <t>116630</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146524</t>
+          <t>146405</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222609</t>
+          <t>220457</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>262948</t>
+          <t>263155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según su salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19009</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23424</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>56733</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61471</t>
+          <t>60615</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100872</t>
+          <t>99267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90263</t>
+          <t>91989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>146458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>40040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90086</t>
+          <t>90213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71375</t>
+          <t>73012</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107042</t>
+          <t>107402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122639</t>
+          <t>122516</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>184538</t>
+          <t>186181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93959</t>
+          <t>95197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24224</t>
+          <t>24671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50700</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51124</t>
+          <t>49072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149853</t>
+          <t>151287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27177</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23536</t>
+          <t>23486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38857</t>
+          <t>39664</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30655</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33822</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49924</t>
+          <t>49357</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13558</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70463</t>
+          <t>70919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128183</t>
+          <t>129687</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>129018</t>
+          <t>128469</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>189335</t>
+          <t>187942</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56727</t>
+          <t>61605</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113477</t>
+          <t>112788</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>100832</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>139835</t>
+          <t>139047</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>179936</t>
+          <t>177327</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>242548</t>
+          <t>241772</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30692</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114978</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32264</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61784</t>
+          <t>61686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>72309</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>181440</t>
+          <t>181935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
